--- a/outputs/season_record.xlsx
+++ b/outputs/season_record.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
@@ -98,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,22 +126,34 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -613,131 +633,143 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>FLA @ NYR</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>NSH @ TBL</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>NSH ML</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>+164</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>+7.9%</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>NSH @ TBL</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FLA ML</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>+146</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>+14.4%</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>NSH +1.5</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>-150</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>+13.7%</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>+0.67u</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>NSH @ TBL</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>OU</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>NSH ML</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>+164</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>+4.3%</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>NSH @ TBL</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>NSH +1.5</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>-150</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>+3.1%</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>UNDER 6.5</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>-104</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>+0.96u</t>
         </is>
       </c>
     </row>
@@ -749,12 +781,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>NSH @ TBL</t>
+          <t>BOS @ CBJ</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -764,109 +796,121 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>UNDER 6.5</t>
+          <t>BOS ML</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>-104</t>
+          <t>+130</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>+4.8%</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
+          <t>+4.2%</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>+1.30u</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>BOS @ CBJ</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>BOS +1.5</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>-192</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>+8.2%</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>+0.52u</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>CHI @ NJD</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BOS ML</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>+134</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>+4.8%</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>BOS @ CBJ</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>BOS +1.5</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>-188</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>+10.2%</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>CHI ML</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>+138</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
         </is>
       </c>
     </row>
@@ -903,56 +947,64 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>+14.2%</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
+          <t>+9.0%</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>DAL @ PHI</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>PHI ML</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>+140</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>+5.9%</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>+11.2%</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>+1.40u</t>
         </is>
       </c>
     </row>
@@ -989,25 +1041,29 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>+4.2%</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
+          <t>+4.5%</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>-1.00u</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>SEASON TOTAL</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>+0.85u</t>
         </is>
       </c>
     </row>
@@ -1040,14 +1096,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>NHL MODEL — SEASON RECORD</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>ALL PICKS (HIGH + MEDIUM)</t>
         </is>
@@ -1096,143 +1152,143 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Moneyline</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
+      <c r="B5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>+0.70u</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>$+7.00</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Puck Line</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
+      <c r="B6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>+0.19u</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>$+1.88</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
+      <c r="B7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>-0.04u</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>$-0.38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve"> COMBINED</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
+      <c r="B8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>+0.85u</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>$+8.50</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>HIGH CONFIDENCE</t>
         </is>
@@ -1281,143 +1337,143 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Moneyline</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="B12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>+1.40u</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>$+14.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Puck Line</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>+0.19u</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>$+1.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>+0.00u</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>$+0.00</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Puck Line</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Over/Under</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
-        </is>
-      </c>
-    </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve"> COMBINED</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
+      <c r="B15" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>+1.59u</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>$+15.88</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>MEDIUM CONFIDENCE</t>
         </is>
@@ -1466,138 +1522,138 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Moneyline</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="B19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>-0.70u</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>$-7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Puck Line</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>+0.00u</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>$+0.00</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Puck Line</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
+      <c r="B21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>-0.04u</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>$-0.38</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve"> COMBINED</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>+0.00u</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>$+0.00</t>
+      <c r="B22" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>-0.74u</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>$-7.38</t>
         </is>
       </c>
     </row>
